--- a/output/pdf_financials_xlsx/MFC.xlsx
+++ b/output/pdf_financials_xlsx/MFC.xlsx
@@ -6309,13 +6309,13 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-98</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-118</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="125">
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-98</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-118</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="126">
@@ -34315,7 +34315,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -46888,7 +46892,7 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E591" s="5" t="n">

--- a/output/pdf_financials_xlsx/MFC.xlsx
+++ b/output/pdf_financials_xlsx/MFC.xlsx
@@ -3208,19 +3208,19 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>5461</v>
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>10107</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>9840</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>9840</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>10097</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>11052</v>
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>12324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5497,19 +5497,19 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0</v>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E328" s="5" t="n">
@@ -32749,7 +32749,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -33277,7 +33281,11 @@
           <t>Deferred income tax expenses (recoveries)</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -35618,7 +35626,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E425" s="5" t="n">
         <v>14</v>
       </c>
@@ -39174,7 +39186,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E477" s="5" t="n">
         <v>98</v>
       </c>
@@ -40177,7 +40193,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
